--- a/data/trans_orig/P34B02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34B02-Edad-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población realiza gimnasia suave juegos que requieren poco esfuerzo y similares</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población realiza gimnasia suave como juegos que requieren poco esfuerzo y similares (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,62</t>
+          <t>0,36; 0,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,75</t>
+          <t>0,46; 0,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,22 +692,22 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,41</t>
+          <t>0,22; 0,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,54</t>
+          <t>0,31; 0,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,42</t>
+          <t>0,87; 1,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,48</t>
+          <t>0,32; 0,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,7</t>
+          <t>1,21; 1,69</t>
         </is>
       </c>
     </row>
@@ -792,27 +792,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,84</t>
+          <t>0,55; 0,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,44</t>
+          <t>0,94; 1,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,34</t>
+          <t>0,16; 0,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,42</t>
+          <t>0,24; 0,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,77</t>
+          <t>0,36; 0,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,6</t>
+          <t>0,44; 0,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,01</t>
+          <t>0,64; 1,03</t>
         </is>
       </c>
     </row>
@@ -897,22 +897,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,42</t>
+          <t>0,25; 0,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,56</t>
+          <t>0,35; 0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,35</t>
+          <t>1,0; 1,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,28</t>
+          <t>0,14; 0,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,95</t>
+          <t>0,7; 0,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,5</t>
+          <t>0,36; 0,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1007,22 +1007,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,41</t>
+          <t>0,23; 0,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,5</t>
+          <t>0,31; 0,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,91</t>
+          <t>0,28; 0,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,34</t>
+          <t>0,15; 0,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,41</t>
+          <t>0,27; 0,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,84</t>
+          <t>0,43; 0,85</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,34</t>
+          <t>0,15; 0,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1127,37 +1127,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,93</t>
+          <t>0,65; 0,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,39</t>
+          <t>0,19; 0,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,38</t>
+          <t>0,16; 0,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,79</t>
+          <t>0,6; 0,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,34</t>
+          <t>0,18; 0,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,35</t>
+          <t>0,2; 0,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,82</t>
+          <t>0,65; 0,83</t>
         </is>
       </c>
     </row>
@@ -1227,22 +1227,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,58</t>
+          <t>0,22; 0,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,39</t>
+          <t>0,14; 0,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,68</t>
+          <t>0,4; 0,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,26</t>
+          <t>0,09; 0,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,6</t>
+          <t>0,16; 0,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,36</t>
+          <t>0,16; 0,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,57</t>
+          <t>0,24; 0,58</t>
         </is>
       </c>
     </row>
@@ -1337,17 +1337,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,27</t>
+          <t>0,04; 0,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,24</t>
+          <t>0,05; 0,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,38</t>
+          <t>0,18; 0,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,26</t>
+          <t>0,06; 0,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,2</t>
+          <t>0,08; 0,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,31</t>
+          <t>0,19; 0,31</t>
         </is>
       </c>
     </row>
@@ -1457,27 +1457,27 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,99</t>
+          <t>0,7; 0,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,25</t>
+          <t>0,19; 0,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,34</t>
+          <t>0,27; 0,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,7</t>
+          <t>0,53; 0,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,3</t>
+          <t>0,24; 0,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,82</t>
+          <t>0,66; 0,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34B02-Edad-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,22 +677,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,61</t>
+          <t>0,36; 0,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,75</t>
+          <t>0,46; 0,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,11</t>
+          <t>1,42; 2,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,41</t>
+          <t>0,22; 0,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,46</t>
+          <t>0,89; 1,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,48</t>
+          <t>0,32; 0,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,61</t>
+          <t>0,42; 0,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,69</t>
+          <t>1,22; 1,65</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,93</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,44</t>
+          <t>0,24; 0,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,82</t>
+          <t>0,57; 0,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,43</t>
+          <t>0,97; 1,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,35</t>
+          <t>0,16; 0,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,43</t>
+          <t>0,24; 0,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,78</t>
+          <t>0,55; 0,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,6</t>
+          <t>0,43; 0,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,03</t>
+          <t>0,8; 1,08</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,43</t>
+          <t>0,26; 0,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,38</t>
+          <t>0,98; 1,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -922,22 +922,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 0,93</t>
+          <t>0,68; 0,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,32</t>
+          <t>0,21; 0,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,51</t>
+          <t>0,36; 0,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,1</t>
+          <t>0,87; 1,07</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -1007,22 +1007,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,42</t>
+          <t>0,22; 0,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,53</t>
+          <t>0,29; 0,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,92</t>
+          <t>0,74; 1,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,33</t>
+          <t>0,15; 0,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,87</t>
+          <t>0,7; 0,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,34</t>
+          <t>0,21; 0,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,85</t>
+          <t>0,73; 0,9</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,22 +1117,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,34</t>
+          <t>0,14; 0,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,4</t>
+          <t>0,19; 0,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,92</t>
+          <t>0,67; 0,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,4</t>
+          <t>0,19; 0,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1142,22 +1142,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,8</t>
+          <t>0,58; 0,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,33</t>
+          <t>0,19; 0,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,35</t>
+          <t>0,19; 0,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,83</t>
+          <t>0,66; 0,83</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,55</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,57</t>
+          <t>0,22; 0,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1237,27 +1237,27 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,67</t>
+          <t>0,42; 0,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,26</t>
+          <t>0,08; 0,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,38</t>
+          <t>0,15; 0,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,61</t>
+          <t>0,46; 0,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,35</t>
+          <t>0,17; 0,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,58</t>
+          <t>0,48; 0,63</t>
         </is>
       </c>
     </row>
@@ -1337,17 +1337,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,27</t>
+          <t>0,05; 0,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,26</t>
+          <t>0,04; 0,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,39</t>
+          <t>0,17; 0,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1357,22 +1357,22 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,23</t>
+          <t>0,07; 0,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,31</t>
+          <t>0,17; 0,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,19</t>
+          <t>0,06; 0,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,2</t>
+          <t>0,08; 0,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -1452,27 +1452,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,47</t>
+          <t>0,38; 0,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 0,98</t>
+          <t>0,88; 1,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,26</t>
+          <t>0,18; 0,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,34</t>
+          <t>0,26; 0,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,7</t>
+          <t>0,65; 0,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,83</t>
+          <t>0,78; 0,86</t>
         </is>
       </c>
     </row>
